--- a/ZLM_Meter_Hierarchy_2026-10-06.xlsx
+++ b/ZLM_Meter_Hierarchy_2026-10-06.xlsx
@@ -15,8 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Issues" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Elec'!$A$1:$Q$885</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kiosks'!$A$1:$Q$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Elec'!$A$1:$Q$930</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kiosks'!$A$1:$Q$192</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Minisubs'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AMR Devices'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Orders'!$A$1:$F$4</definedName>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q885"/>
+  <dimension ref="A1:Q930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12662,12 +12662,26 @@
         </is>
       </c>
       <c r="J208" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K208" s="2" t="inlineStr"/>
-      <c r="L208" s="2" t="inlineStr"/>
-      <c r="M208" s="2" t="inlineStr"/>
-      <c r="N208" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105981</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 186 [Elec]</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:26 AM</t>
+        </is>
+      </c>
       <c r="O208" s="2" t="inlineStr"/>
       <c r="P208" s="2" t="inlineStr">
         <is>
@@ -12721,12 +12735,26 @@
         </is>
       </c>
       <c r="J209" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K209" s="2" t="inlineStr"/>
-      <c r="L209" s="2" t="inlineStr"/>
-      <c r="M209" s="2" t="inlineStr"/>
-      <c r="N209" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105981</t>
+        </is>
+      </c>
+      <c r="L209" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 187 [Elec]</t>
+        </is>
+      </c>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:26 AM</t>
+        </is>
+      </c>
       <c r="O209" s="2" t="inlineStr"/>
       <c r="P209" s="2" t="inlineStr">
         <is>
@@ -12780,12 +12808,26 @@
         </is>
       </c>
       <c r="J210" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K210" s="2" t="inlineStr"/>
-      <c r="L210" s="2" t="inlineStr"/>
-      <c r="M210" s="2" t="inlineStr"/>
-      <c r="N210" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105981</t>
+        </is>
+      </c>
+      <c r="L210" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 188 [Elec]</t>
+        </is>
+      </c>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:26 AM</t>
+        </is>
+      </c>
       <c r="O210" s="2" t="inlineStr"/>
       <c r="P210" s="2" t="inlineStr">
         <is>
@@ -12839,12 +12881,26 @@
         </is>
       </c>
       <c r="J211" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K211" s="2" t="inlineStr"/>
-      <c r="L211" s="2" t="inlineStr"/>
-      <c r="M211" s="2" t="inlineStr"/>
-      <c r="N211" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105981</t>
+        </is>
+      </c>
+      <c r="L211" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 190 [Elec]</t>
+        </is>
+      </c>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>10/1/2026, 12:19 PM</t>
+        </is>
+      </c>
       <c r="O211" s="2" t="inlineStr"/>
       <c r="P211" s="2" t="inlineStr">
         <is>
@@ -12898,12 +12954,26 @@
         </is>
       </c>
       <c r="J212" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K212" s="2" t="inlineStr"/>
-      <c r="L212" s="2" t="inlineStr"/>
-      <c r="M212" s="2" t="inlineStr"/>
-      <c r="N212" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105981</t>
+        </is>
+      </c>
+      <c r="L212" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 191 [Elec]</t>
+        </is>
+      </c>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:26 AM</t>
+        </is>
+      </c>
       <c r="O212" s="2" t="inlineStr"/>
       <c r="P212" s="2" t="inlineStr">
         <is>
@@ -14341,12 +14411,26 @@
         </is>
       </c>
       <c r="J237" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K237" s="2" t="inlineStr"/>
-      <c r="L237" s="2" t="inlineStr"/>
-      <c r="M237" s="2" t="inlineStr"/>
-      <c r="N237" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K237" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350013b</t>
+        </is>
+      </c>
+      <c r="L237" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 179 [Elec]</t>
+        </is>
+      </c>
+      <c r="N237" s="2" t="inlineStr">
+        <is>
+          <t>9/22/2026, 09:00 AM</t>
+        </is>
+      </c>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
@@ -14400,12 +14484,26 @@
         </is>
       </c>
       <c r="J238" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K238" s="2" t="inlineStr"/>
-      <c r="L238" s="2" t="inlineStr"/>
-      <c r="M238" s="2" t="inlineStr"/>
-      <c r="N238" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K238" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350013b</t>
+        </is>
+      </c>
+      <c r="L238" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M238" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 180 [Elec]</t>
+        </is>
+      </c>
+      <c r="N238" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:46 AM</t>
+        </is>
+      </c>
       <c r="O238" s="2" t="inlineStr"/>
       <c r="P238" s="2" t="inlineStr">
         <is>
@@ -14459,12 +14557,26 @@
         </is>
       </c>
       <c r="J239" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K239" s="2" t="inlineStr"/>
-      <c r="L239" s="2" t="inlineStr"/>
-      <c r="M239" s="2" t="inlineStr"/>
-      <c r="N239" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K239" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350013b</t>
+        </is>
+      </c>
+      <c r="L239" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M239" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 184 [Elec]</t>
+        </is>
+      </c>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:46 AM</t>
+        </is>
+      </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
@@ -14518,12 +14630,26 @@
         </is>
       </c>
       <c r="J240" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K240" s="2" t="inlineStr"/>
-      <c r="L240" s="2" t="inlineStr"/>
-      <c r="M240" s="2" t="inlineStr"/>
-      <c r="N240" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350013b</t>
+        </is>
+      </c>
+      <c r="L240" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 194 [Elec]</t>
+        </is>
+      </c>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>9/22/2026, 09:00 AM</t>
+        </is>
+      </c>
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr">
         <is>
@@ -14577,12 +14703,26 @@
         </is>
       </c>
       <c r="J241" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K241" s="2" t="inlineStr"/>
-      <c r="L241" s="2" t="inlineStr"/>
-      <c r="M241" s="2" t="inlineStr"/>
-      <c r="N241" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K241" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350013b</t>
+        </is>
+      </c>
+      <c r="L241" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 195 [Elec]</t>
+        </is>
+      </c>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>9/22/2026, 03:55 PM</t>
+        </is>
+      </c>
       <c r="O241" s="2" t="inlineStr"/>
       <c r="P241" s="2" t="inlineStr">
         <is>
@@ -14693,12 +14833,26 @@
         </is>
       </c>
       <c r="J243" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K243" s="2" t="inlineStr"/>
-      <c r="L243" s="2" t="inlineStr"/>
-      <c r="M243" s="2" t="inlineStr"/>
-      <c r="N243" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K243" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350013b</t>
+        </is>
+      </c>
+      <c r="L243" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 197 [Elec]</t>
+        </is>
+      </c>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>9/22/2026, 02:55 PM</t>
+        </is>
+      </c>
       <c r="O243" s="2" t="inlineStr"/>
       <c r="P243" s="2" t="inlineStr">
         <is>
@@ -14752,12 +14906,26 @@
         </is>
       </c>
       <c r="J244" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K244" s="2" t="inlineStr"/>
-      <c r="L244" s="2" t="inlineStr"/>
-      <c r="M244" s="2" t="inlineStr"/>
-      <c r="N244" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350013b</t>
+        </is>
+      </c>
+      <c r="L244" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 201 [Elec]</t>
+        </is>
+      </c>
+      <c r="N244" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:46 AM</t>
+        </is>
+      </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
@@ -15210,12 +15378,26 @@
         </is>
       </c>
       <c r="J252" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K252" s="2" t="inlineStr"/>
-      <c r="L252" s="2" t="inlineStr"/>
-      <c r="M252" s="2" t="inlineStr"/>
-      <c r="N252" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641067ff</t>
+        </is>
+      </c>
+      <c r="L252" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 175 [Elec]</t>
+        </is>
+      </c>
+      <c r="N252" s="2" t="inlineStr">
+        <is>
+          <t>9/22/2026, 03:43 PM</t>
+        </is>
+      </c>
       <c r="O252" s="2" t="inlineStr"/>
       <c r="P252" s="2" t="inlineStr">
         <is>
@@ -15269,12 +15451,26 @@
         </is>
       </c>
       <c r="J253" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K253" s="2" t="inlineStr"/>
-      <c r="L253" s="2" t="inlineStr"/>
-      <c r="M253" s="2" t="inlineStr"/>
-      <c r="N253" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K253" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641067ff</t>
+        </is>
+      </c>
+      <c r="L253" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M253" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 176 [Elec]</t>
+        </is>
+      </c>
+      <c r="N253" s="2" t="inlineStr">
+        <is>
+          <t>9/22/2026, 03:44 PM</t>
+        </is>
+      </c>
       <c r="O253" s="2" t="inlineStr"/>
       <c r="P253" s="2" t="inlineStr">
         <is>
@@ -15328,12 +15524,26 @@
         </is>
       </c>
       <c r="J254" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K254" s="2" t="inlineStr"/>
-      <c r="L254" s="2" t="inlineStr"/>
-      <c r="M254" s="2" t="inlineStr"/>
-      <c r="N254" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K254" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641067ff</t>
+        </is>
+      </c>
+      <c r="L254" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M254" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 177 [Elec]</t>
+        </is>
+      </c>
+      <c r="N254" s="2" t="inlineStr">
+        <is>
+          <t>9/22/2026, 03:43 PM</t>
+        </is>
+      </c>
       <c r="O254" s="2" t="inlineStr"/>
       <c r="P254" s="2" t="inlineStr">
         <is>
@@ -15387,12 +15597,26 @@
         </is>
       </c>
       <c r="J255" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K255" s="2" t="inlineStr"/>
-      <c r="L255" s="2" t="inlineStr"/>
-      <c r="M255" s="2" t="inlineStr"/>
-      <c r="N255" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K255" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641067ff</t>
+        </is>
+      </c>
+      <c r="L255" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M255" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 178 [Elec]</t>
+        </is>
+      </c>
+      <c r="N255" s="2" t="inlineStr">
+        <is>
+          <t>9/22/2026, 03:43 PM</t>
+        </is>
+      </c>
       <c r="O255" s="2" t="inlineStr"/>
       <c r="P255" s="2" t="inlineStr">
         <is>
@@ -15446,12 +15670,26 @@
         </is>
       </c>
       <c r="J256" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K256" s="2" t="inlineStr"/>
-      <c r="L256" s="2" t="inlineStr"/>
-      <c r="M256" s="2" t="inlineStr"/>
-      <c r="N256" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641067ff</t>
+        </is>
+      </c>
+      <c r="L256" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 181 [Elec]</t>
+        </is>
+      </c>
+      <c r="N256" s="2" t="inlineStr">
+        <is>
+          <t>9/22/2026, 03:43 PM</t>
+        </is>
+      </c>
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
@@ -15562,12 +15800,26 @@
         </is>
       </c>
       <c r="J258" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K258" s="2" t="inlineStr"/>
-      <c r="L258" s="2" t="inlineStr"/>
-      <c r="M258" s="2" t="inlineStr"/>
-      <c r="N258" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641060c2</t>
+        </is>
+      </c>
+      <c r="L258" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M258" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 135 [Elec]</t>
+        </is>
+      </c>
+      <c r="N258" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:16 AM</t>
+        </is>
+      </c>
       <c r="O258" s="2" t="inlineStr"/>
       <c r="P258" s="2" t="inlineStr">
         <is>
@@ -15621,12 +15873,26 @@
         </is>
       </c>
       <c r="J259" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K259" s="2" t="inlineStr"/>
-      <c r="L259" s="2" t="inlineStr"/>
-      <c r="M259" s="2" t="inlineStr"/>
-      <c r="N259" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K259" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641060c2</t>
+        </is>
+      </c>
+      <c r="L259" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 136 [Elec]</t>
+        </is>
+      </c>
+      <c r="N259" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:16 AM</t>
+        </is>
+      </c>
       <c r="O259" s="2" t="inlineStr"/>
       <c r="P259" s="2" t="inlineStr">
         <is>
@@ -15680,12 +15946,26 @@
         </is>
       </c>
       <c r="J260" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K260" s="2" t="inlineStr"/>
-      <c r="L260" s="2" t="inlineStr"/>
-      <c r="M260" s="2" t="inlineStr"/>
-      <c r="N260" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K260" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641060c2</t>
+        </is>
+      </c>
+      <c r="L260" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M260" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 154 [Elec]</t>
+        </is>
+      </c>
+      <c r="N260" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:16 AM</t>
+        </is>
+      </c>
       <c r="O260" s="2" t="inlineStr"/>
       <c r="P260" s="2" t="inlineStr">
         <is>
@@ -15739,12 +16019,26 @@
         </is>
       </c>
       <c r="J261" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K261" s="2" t="inlineStr"/>
-      <c r="L261" s="2" t="inlineStr"/>
-      <c r="M261" s="2" t="inlineStr"/>
-      <c r="N261" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K261" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641060c2</t>
+        </is>
+      </c>
+      <c r="L261" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M261" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 155 [Elec]</t>
+        </is>
+      </c>
+      <c r="N261" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:16 AM</t>
+        </is>
+      </c>
       <c r="O261" s="2" t="inlineStr"/>
       <c r="P261" s="2" t="inlineStr">
         <is>
@@ -16081,12 +16375,26 @@
         </is>
       </c>
       <c r="J267" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K267" s="2" t="inlineStr"/>
-      <c r="L267" s="2" t="inlineStr"/>
-      <c r="M267" s="2" t="inlineStr"/>
-      <c r="N267" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K267" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063400e34</t>
+        </is>
+      </c>
+      <c r="L267" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 202 [Elec]</t>
+        </is>
+      </c>
+      <c r="N267" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:28 AM</t>
+        </is>
+      </c>
       <c r="O267" s="2" t="inlineStr"/>
       <c r="P267" s="2" t="inlineStr">
         <is>
@@ -16140,12 +16448,26 @@
         </is>
       </c>
       <c r="J268" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K268" s="2" t="inlineStr"/>
-      <c r="L268" s="2" t="inlineStr"/>
-      <c r="M268" s="2" t="inlineStr"/>
-      <c r="N268" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K268" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063400e34</t>
+        </is>
+      </c>
+      <c r="L268" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M268" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 203 [Elec]</t>
+        </is>
+      </c>
+      <c r="N268" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:28 AM</t>
+        </is>
+      </c>
       <c r="O268" s="2" t="inlineStr"/>
       <c r="P268" s="2" t="inlineStr">
         <is>
@@ -16199,12 +16521,26 @@
         </is>
       </c>
       <c r="J269" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K269" s="2" t="inlineStr"/>
-      <c r="L269" s="2" t="inlineStr"/>
-      <c r="M269" s="2" t="inlineStr"/>
-      <c r="N269" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K269" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063400e34</t>
+        </is>
+      </c>
+      <c r="L269" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M269" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 204 [Elec]</t>
+        </is>
+      </c>
+      <c r="N269" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:28 AM</t>
+        </is>
+      </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
@@ -16258,12 +16594,26 @@
         </is>
       </c>
       <c r="J270" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K270" s="2" t="inlineStr"/>
-      <c r="L270" s="2" t="inlineStr"/>
-      <c r="M270" s="2" t="inlineStr"/>
-      <c r="N270" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K270" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063400e34</t>
+        </is>
+      </c>
+      <c r="L270" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M270" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 205 [Elec]</t>
+        </is>
+      </c>
+      <c r="N270" s="2" t="inlineStr">
+        <is>
+          <t>7/24/2026, 02:06 PM</t>
+        </is>
+      </c>
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr">
         <is>
@@ -18784,12 +19134,26 @@
         </is>
       </c>
       <c r="J314" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K314" s="2" t="inlineStr"/>
-      <c r="L314" s="2" t="inlineStr"/>
-      <c r="M314" s="2" t="inlineStr"/>
-      <c r="N314" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K314" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063502165</t>
+        </is>
+      </c>
+      <c r="L314" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M314" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 38 [Elec]</t>
+        </is>
+      </c>
+      <c r="N314" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:21 AM</t>
+        </is>
+      </c>
       <c r="O314" s="2" t="inlineStr"/>
       <c r="P314" s="2" t="inlineStr">
         <is>
@@ -18957,12 +19321,26 @@
         </is>
       </c>
       <c r="J317" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K317" s="2" t="inlineStr"/>
-      <c r="L317" s="2" t="inlineStr"/>
-      <c r="M317" s="2" t="inlineStr"/>
-      <c r="N317" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K317" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063502165</t>
+        </is>
+      </c>
+      <c r="L317" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M317" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 88 [Elec]</t>
+        </is>
+      </c>
+      <c r="N317" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:21 AM</t>
+        </is>
+      </c>
       <c r="O317" s="2" t="inlineStr"/>
       <c r="P317" s="2" t="inlineStr">
         <is>
@@ -19016,12 +19394,26 @@
         </is>
       </c>
       <c r="J318" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K318" s="2" t="inlineStr"/>
-      <c r="L318" s="2" t="inlineStr"/>
-      <c r="M318" s="2" t="inlineStr"/>
-      <c r="N318" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K318" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063502165</t>
+        </is>
+      </c>
+      <c r="L318" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M318" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 89 [Elec]</t>
+        </is>
+      </c>
+      <c r="N318" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:21 AM</t>
+        </is>
+      </c>
       <c r="O318" s="2" t="inlineStr"/>
       <c r="P318" s="2" t="inlineStr">
         <is>
@@ -19075,12 +19467,26 @@
         </is>
       </c>
       <c r="J319" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K319" s="2" t="inlineStr"/>
-      <c r="L319" s="2" t="inlineStr"/>
-      <c r="M319" s="2" t="inlineStr"/>
-      <c r="N319" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K319" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063502165</t>
+        </is>
+      </c>
+      <c r="L319" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M319" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 90 [Elec]</t>
+        </is>
+      </c>
+      <c r="N319" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:21 AM</t>
+        </is>
+      </c>
       <c r="O319" s="2" t="inlineStr"/>
       <c r="P319" s="2" t="inlineStr">
         <is>
@@ -19362,12 +19768,26 @@
         </is>
       </c>
       <c r="J324" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K324" s="2" t="inlineStr"/>
-      <c r="L324" s="2" t="inlineStr"/>
-      <c r="M324" s="2" t="inlineStr"/>
-      <c r="N324" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K324" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105879</t>
+        </is>
+      </c>
+      <c r="L324" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M324" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 64 [Elec]</t>
+        </is>
+      </c>
+      <c r="N324" s="2" t="inlineStr">
+        <is>
+          <t>6/12/2026, 03:03 PM</t>
+        </is>
+      </c>
       <c r="O324" s="2" t="inlineStr"/>
       <c r="P324" s="2" t="inlineStr">
         <is>
@@ -19421,12 +19841,26 @@
         </is>
       </c>
       <c r="J325" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K325" s="2" t="inlineStr"/>
-      <c r="L325" s="2" t="inlineStr"/>
-      <c r="M325" s="2" t="inlineStr"/>
-      <c r="N325" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K325" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105879</t>
+        </is>
+      </c>
+      <c r="L325" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M325" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 65 [Elec]</t>
+        </is>
+      </c>
+      <c r="N325" s="2" t="inlineStr">
+        <is>
+          <t>6/12/2026, 03:03 PM</t>
+        </is>
+      </c>
       <c r="O325" s="2" t="inlineStr"/>
       <c r="P325" s="2" t="inlineStr">
         <is>
@@ -19480,12 +19914,26 @@
         </is>
       </c>
       <c r="J326" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K326" s="2" t="inlineStr"/>
-      <c r="L326" s="2" t="inlineStr"/>
-      <c r="M326" s="2" t="inlineStr"/>
-      <c r="N326" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K326" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105879</t>
+        </is>
+      </c>
+      <c r="L326" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M326" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 66 [Elec]</t>
+        </is>
+      </c>
+      <c r="N326" s="2" t="inlineStr">
+        <is>
+          <t>6/12/2026, 03:03 PM</t>
+        </is>
+      </c>
       <c r="O326" s="2" t="inlineStr"/>
       <c r="P326" s="2" t="inlineStr">
         <is>
@@ -19828,12 +20276,26 @@
         </is>
       </c>
       <c r="J332" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K332" s="2" t="inlineStr"/>
-      <c r="L332" s="2" t="inlineStr"/>
-      <c r="M332" s="2" t="inlineStr"/>
-      <c r="N332" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K332" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063101a76</t>
+        </is>
+      </c>
+      <c r="L332" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M332" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 91 [Elec]</t>
+        </is>
+      </c>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:43 AM</t>
+        </is>
+      </c>
       <c r="O332" s="2" t="inlineStr"/>
       <c r="P332" s="2" t="inlineStr">
         <is>
@@ -19887,12 +20349,26 @@
         </is>
       </c>
       <c r="J333" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K333" s="2" t="inlineStr"/>
-      <c r="L333" s="2" t="inlineStr"/>
-      <c r="M333" s="2" t="inlineStr"/>
-      <c r="N333" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K333" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063101a76</t>
+        </is>
+      </c>
+      <c r="L333" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M333" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 92 [Elec]</t>
+        </is>
+      </c>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:43 AM</t>
+        </is>
+      </c>
       <c r="O333" s="2" t="inlineStr"/>
       <c r="P333" s="2" t="inlineStr">
         <is>
@@ -19946,12 +20422,26 @@
         </is>
       </c>
       <c r="J334" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K334" s="2" t="inlineStr"/>
-      <c r="L334" s="2" t="inlineStr"/>
-      <c r="M334" s="2" t="inlineStr"/>
-      <c r="N334" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K334" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063101a76</t>
+        </is>
+      </c>
+      <c r="L334" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M334" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 93 [Elec]</t>
+        </is>
+      </c>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:43 AM</t>
+        </is>
+      </c>
       <c r="O334" s="2" t="inlineStr"/>
       <c r="P334" s="2" t="inlineStr">
         <is>
@@ -20634,12 +21124,26 @@
         </is>
       </c>
       <c r="J346" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K346" s="2" t="inlineStr"/>
-      <c r="L346" s="2" t="inlineStr"/>
-      <c r="M346" s="2" t="inlineStr"/>
-      <c r="N346" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K346" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635025eb</t>
+        </is>
+      </c>
+      <c r="L346" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M346" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 67 [Elec]</t>
+        </is>
+      </c>
+      <c r="N346" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:13 AM</t>
+        </is>
+      </c>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
@@ -20693,12 +21197,26 @@
         </is>
       </c>
       <c r="J347" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K347" s="2" t="inlineStr"/>
-      <c r="L347" s="2" t="inlineStr"/>
-      <c r="M347" s="2" t="inlineStr"/>
-      <c r="N347" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K347" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635025eb</t>
+        </is>
+      </c>
+      <c r="L347" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M347" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 68 [Elec]</t>
+        </is>
+      </c>
+      <c r="N347" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:13 AM</t>
+        </is>
+      </c>
       <c r="O347" s="2" t="inlineStr"/>
       <c r="P347" s="2" t="inlineStr">
         <is>
@@ -20752,12 +21270,26 @@
         </is>
       </c>
       <c r="J348" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K348" s="2" t="inlineStr"/>
-      <c r="L348" s="2" t="inlineStr"/>
-      <c r="M348" s="2" t="inlineStr"/>
-      <c r="N348" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K348" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635025eb</t>
+        </is>
+      </c>
+      <c r="L348" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M348" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 69 [Elec]</t>
+        </is>
+      </c>
+      <c r="N348" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:13 AM</t>
+        </is>
+      </c>
       <c r="O348" s="2" t="inlineStr"/>
       <c r="P348" s="2" t="inlineStr">
         <is>
@@ -20811,12 +21343,26 @@
         </is>
       </c>
       <c r="J349" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K349" s="2" t="inlineStr"/>
-      <c r="L349" s="2" t="inlineStr"/>
-      <c r="M349" s="2" t="inlineStr"/>
-      <c r="N349" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K349" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635025eb</t>
+        </is>
+      </c>
+      <c r="L349" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M349" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 70 [Elec]</t>
+        </is>
+      </c>
+      <c r="N349" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:13 AM</t>
+        </is>
+      </c>
       <c r="O349" s="2" t="inlineStr"/>
       <c r="P349" s="2" t="inlineStr">
         <is>
@@ -20870,12 +21416,26 @@
         </is>
       </c>
       <c r="J350" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K350" s="2" t="inlineStr"/>
-      <c r="L350" s="2" t="inlineStr"/>
-      <c r="M350" s="2" t="inlineStr"/>
-      <c r="N350" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K350" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635025eb</t>
+        </is>
+      </c>
+      <c r="L350" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M350" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 71 [Elec]</t>
+        </is>
+      </c>
+      <c r="N350" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:13 AM</t>
+        </is>
+      </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
@@ -20929,12 +21489,26 @@
         </is>
       </c>
       <c r="J351" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K351" s="2" t="inlineStr"/>
-      <c r="L351" s="2" t="inlineStr"/>
-      <c r="M351" s="2" t="inlineStr"/>
-      <c r="N351" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K351" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635025eb</t>
+        </is>
+      </c>
+      <c r="L351" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M351" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 72 [Elec]</t>
+        </is>
+      </c>
+      <c r="N351" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:13 AM</t>
+        </is>
+      </c>
       <c r="O351" s="2" t="inlineStr"/>
       <c r="P351" s="2" t="inlineStr">
         <is>
@@ -21102,12 +21676,26 @@
         </is>
       </c>
       <c r="J354" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K354" s="2" t="inlineStr"/>
-      <c r="L354" s="2" t="inlineStr"/>
-      <c r="M354" s="2" t="inlineStr"/>
-      <c r="N354" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K354" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063101c2a</t>
+        </is>
+      </c>
+      <c r="L354" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M354" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 94 [Elec]</t>
+        </is>
+      </c>
+      <c r="N354" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:32 AM</t>
+        </is>
+      </c>
       <c r="O354" s="2" t="inlineStr"/>
       <c r="P354" s="2" t="inlineStr">
         <is>
@@ -21161,12 +21749,26 @@
         </is>
       </c>
       <c r="J355" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K355" s="2" t="inlineStr"/>
-      <c r="L355" s="2" t="inlineStr"/>
-      <c r="M355" s="2" t="inlineStr"/>
-      <c r="N355" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K355" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063101c2a</t>
+        </is>
+      </c>
+      <c r="L355" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M355" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 95 [Elec]</t>
+        </is>
+      </c>
+      <c r="N355" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:32 AM</t>
+        </is>
+      </c>
       <c r="O355" s="2" t="inlineStr"/>
       <c r="P355" s="2" t="inlineStr">
         <is>
@@ -21220,12 +21822,26 @@
         </is>
       </c>
       <c r="J356" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K356" s="2" t="inlineStr"/>
-      <c r="L356" s="2" t="inlineStr"/>
-      <c r="M356" s="2" t="inlineStr"/>
-      <c r="N356" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K356" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063101c2a</t>
+        </is>
+      </c>
+      <c r="L356" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M356" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 96 [Elec]</t>
+        </is>
+      </c>
+      <c r="N356" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:32 AM</t>
+        </is>
+      </c>
       <c r="O356" s="2" t="inlineStr"/>
       <c r="P356" s="2" t="inlineStr">
         <is>
@@ -21279,12 +21895,26 @@
         </is>
       </c>
       <c r="J357" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K357" s="2" t="inlineStr"/>
-      <c r="L357" s="2" t="inlineStr"/>
-      <c r="M357" s="2" t="inlineStr"/>
-      <c r="N357" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K357" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063101c2a</t>
+        </is>
+      </c>
+      <c r="L357" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M357" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 97 [Elec]</t>
+        </is>
+      </c>
+      <c r="N357" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:32 AM</t>
+        </is>
+      </c>
       <c r="O357" s="2" t="inlineStr"/>
       <c r="P357" s="2" t="inlineStr">
         <is>
@@ -21338,12 +21968,26 @@
         </is>
       </c>
       <c r="J358" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K358" s="2" t="inlineStr"/>
-      <c r="L358" s="2" t="inlineStr"/>
-      <c r="M358" s="2" t="inlineStr"/>
-      <c r="N358" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K358" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063101c2a</t>
+        </is>
+      </c>
+      <c r="L358" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M358" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 98 [Elec]</t>
+        </is>
+      </c>
+      <c r="N358" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:32 AM</t>
+        </is>
+      </c>
       <c r="O358" s="2" t="inlineStr"/>
       <c r="P358" s="2" t="inlineStr">
         <is>
@@ -22311,12 +22955,26 @@
         </is>
       </c>
       <c r="J375" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K375" s="2" t="inlineStr"/>
-      <c r="L375" s="2" t="inlineStr"/>
-      <c r="M375" s="2" t="inlineStr"/>
-      <c r="N375" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K375" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063100f76</t>
+        </is>
+      </c>
+      <c r="L375" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M375" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 99 [Elec]</t>
+        </is>
+      </c>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:42 AM</t>
+        </is>
+      </c>
       <c r="O375" s="2" t="inlineStr"/>
       <c r="P375" s="2" t="inlineStr">
         <is>
@@ -22370,12 +23028,26 @@
         </is>
       </c>
       <c r="J376" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K376" s="2" t="inlineStr"/>
-      <c r="L376" s="2" t="inlineStr"/>
-      <c r="M376" s="2" t="inlineStr"/>
-      <c r="N376" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K376" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063100f76</t>
+        </is>
+      </c>
+      <c r="L376" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M376" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 100 [Elec]</t>
+        </is>
+      </c>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:42 AM</t>
+        </is>
+      </c>
       <c r="O376" s="2" t="inlineStr"/>
       <c r="P376" s="2" t="inlineStr">
         <is>
@@ -22429,12 +23101,26 @@
         </is>
       </c>
       <c r="J377" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K377" s="2" t="inlineStr"/>
-      <c r="L377" s="2" t="inlineStr"/>
-      <c r="M377" s="2" t="inlineStr"/>
-      <c r="N377" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K377" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063100f76</t>
+        </is>
+      </c>
+      <c r="L377" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M377" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 101 [Elec]</t>
+        </is>
+      </c>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:42 AM</t>
+        </is>
+      </c>
       <c r="O377" s="2" t="inlineStr"/>
       <c r="P377" s="2" t="inlineStr">
         <is>
@@ -22488,12 +23174,26 @@
         </is>
       </c>
       <c r="J378" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K378" s="2" t="inlineStr"/>
-      <c r="L378" s="2" t="inlineStr"/>
-      <c r="M378" s="2" t="inlineStr"/>
-      <c r="N378" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K378" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063100f76</t>
+        </is>
+      </c>
+      <c r="L378" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M378" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 102 [Elec]</t>
+        </is>
+      </c>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:42 AM</t>
+        </is>
+      </c>
       <c r="O378" s="2" t="inlineStr"/>
       <c r="P378" s="2" t="inlineStr">
         <is>
@@ -22889,12 +23589,26 @@
         </is>
       </c>
       <c r="J385" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K385" s="2" t="inlineStr"/>
-      <c r="L385" s="2" t="inlineStr"/>
-      <c r="M385" s="2" t="inlineStr"/>
-      <c r="N385" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K385" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063102063</t>
+        </is>
+      </c>
+      <c r="L385" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M385" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 107 [Elec]</t>
+        </is>
+      </c>
+      <c r="N385" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:32 AM</t>
+        </is>
+      </c>
       <c r="O385" s="2" t="inlineStr"/>
       <c r="P385" s="2" t="inlineStr">
         <is>
@@ -22948,12 +23662,26 @@
         </is>
       </c>
       <c r="J386" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K386" s="2" t="inlineStr"/>
-      <c r="L386" s="2" t="inlineStr"/>
-      <c r="M386" s="2" t="inlineStr"/>
-      <c r="N386" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K386" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063102063</t>
+        </is>
+      </c>
+      <c r="L386" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M386" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 108 [Elec]</t>
+        </is>
+      </c>
+      <c r="N386" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:32 AM</t>
+        </is>
+      </c>
       <c r="O386" s="2" t="inlineStr"/>
       <c r="P386" s="2" t="inlineStr">
         <is>
@@ -23007,12 +23735,26 @@
         </is>
       </c>
       <c r="J387" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K387" s="2" t="inlineStr"/>
-      <c r="L387" s="2" t="inlineStr"/>
-      <c r="M387" s="2" t="inlineStr"/>
-      <c r="N387" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K387" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063102063</t>
+        </is>
+      </c>
+      <c r="L387" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M387" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 109 [Elec]</t>
+        </is>
+      </c>
+      <c r="N387" s="2" t="inlineStr">
+        <is>
+          <t>10/7/2026, 11:16 AM</t>
+        </is>
+      </c>
       <c r="O387" s="2" t="inlineStr"/>
       <c r="P387" s="2" t="inlineStr">
         <is>
@@ -23066,12 +23808,26 @@
         </is>
       </c>
       <c r="J388" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K388" s="2" t="inlineStr"/>
-      <c r="L388" s="2" t="inlineStr"/>
-      <c r="M388" s="2" t="inlineStr"/>
-      <c r="N388" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K388" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12063102063</t>
+        </is>
+      </c>
+      <c r="L388" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M388" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 110 [Elec]</t>
+        </is>
+      </c>
+      <c r="N388" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:32 AM</t>
+        </is>
+      </c>
       <c r="O388" s="2" t="inlineStr"/>
       <c r="P388" s="2" t="inlineStr">
         <is>
@@ -24037,12 +24793,26 @@
         </is>
       </c>
       <c r="J405" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K405" s="2" t="inlineStr"/>
-      <c r="L405" s="2" t="inlineStr"/>
-      <c r="M405" s="2" t="inlineStr"/>
-      <c r="N405" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K405" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635002db</t>
+        </is>
+      </c>
+      <c r="L405" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M405" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 73 [Elec]</t>
+        </is>
+      </c>
+      <c r="N405" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:23 AM</t>
+        </is>
+      </c>
       <c r="O405" s="2" t="inlineStr"/>
       <c r="P405" s="2" t="inlineStr">
         <is>
@@ -24096,12 +24866,26 @@
         </is>
       </c>
       <c r="J406" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K406" s="2" t="inlineStr"/>
-      <c r="L406" s="2" t="inlineStr"/>
-      <c r="M406" s="2" t="inlineStr"/>
-      <c r="N406" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K406" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635002db</t>
+        </is>
+      </c>
+      <c r="L406" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M406" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 74 [Elec]</t>
+        </is>
+      </c>
+      <c r="N406" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:23 AM</t>
+        </is>
+      </c>
       <c r="O406" s="2" t="inlineStr"/>
       <c r="P406" s="2" t="inlineStr">
         <is>
@@ -24782,12 +25566,26 @@
         </is>
       </c>
       <c r="J418" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K418" s="2" t="inlineStr"/>
-      <c r="L418" s="2" t="inlineStr"/>
-      <c r="M418" s="2" t="inlineStr"/>
-      <c r="N418" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K418" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641066ca</t>
+        </is>
+      </c>
+      <c r="L418" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M418" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 75 [Elec]</t>
+        </is>
+      </c>
+      <c r="N418" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:44 AM</t>
+        </is>
+      </c>
       <c r="O418" s="2" t="inlineStr"/>
       <c r="P418" s="2" t="inlineStr">
         <is>
@@ -24841,12 +25639,26 @@
         </is>
       </c>
       <c r="J419" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K419" s="2" t="inlineStr"/>
-      <c r="L419" s="2" t="inlineStr"/>
-      <c r="M419" s="2" t="inlineStr"/>
-      <c r="N419" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K419" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641066ca</t>
+        </is>
+      </c>
+      <c r="L419" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M419" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 103 [Elec]</t>
+        </is>
+      </c>
+      <c r="N419" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:44 AM</t>
+        </is>
+      </c>
       <c r="O419" s="2" t="inlineStr"/>
       <c r="P419" s="2" t="inlineStr">
         <is>
@@ -24900,12 +25712,26 @@
         </is>
       </c>
       <c r="J420" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K420" s="2" t="inlineStr"/>
-      <c r="L420" s="2" t="inlineStr"/>
-      <c r="M420" s="2" t="inlineStr"/>
-      <c r="N420" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K420" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641066ca</t>
+        </is>
+      </c>
+      <c r="L420" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M420" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 104 [Elec]</t>
+        </is>
+      </c>
+      <c r="N420" s="2" t="inlineStr">
+        <is>
+          <t>9/29/2026, 04:28 PM</t>
+        </is>
+      </c>
       <c r="O420" s="2" t="inlineStr"/>
       <c r="P420" s="2" t="inlineStr">
         <is>
@@ -24959,12 +25785,26 @@
         </is>
       </c>
       <c r="J421" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K421" s="2" t="inlineStr"/>
-      <c r="L421" s="2" t="inlineStr"/>
-      <c r="M421" s="2" t="inlineStr"/>
-      <c r="N421" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K421" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641066ca</t>
+        </is>
+      </c>
+      <c r="L421" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M421" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 105 [Elec]</t>
+        </is>
+      </c>
+      <c r="N421" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:44 AM</t>
+        </is>
+      </c>
       <c r="O421" s="2" t="inlineStr"/>
       <c r="P421" s="2" t="inlineStr">
         <is>
@@ -25018,12 +25858,26 @@
         </is>
       </c>
       <c r="J422" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K422" s="2" t="inlineStr"/>
-      <c r="L422" s="2" t="inlineStr"/>
-      <c r="M422" s="2" t="inlineStr"/>
-      <c r="N422" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K422" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120641066ca</t>
+        </is>
+      </c>
+      <c r="L422" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M422" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove 106 [Elec]</t>
+        </is>
+      </c>
+      <c r="N422" s="2" t="inlineStr">
+        <is>
+          <t>9/29/2026, 04:28 PM</t>
+        </is>
+      </c>
       <c r="O422" s="2" t="inlineStr"/>
       <c r="P422" s="2" t="inlineStr">
         <is>
@@ -53473,8 +54327,3113 @@
         </is>
       </c>
     </row>
+    <row r="886">
+      <c r="A886" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0885</t>
+        </is>
+      </c>
+      <c r="B886" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C886" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D886" s="2" t="inlineStr">
+        <is>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="E886" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F886" s="2" t="inlineStr"/>
+      <c r="G886" s="2" t="inlineStr"/>
+      <c r="H886" s="2" t="n">
+        <v>91732634</v>
+      </c>
+      <c r="I886" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J886" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K886" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105bd5</t>
+        </is>
+      </c>
+      <c r="L886" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M886" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B001 [Elec]</t>
+        </is>
+      </c>
+      <c r="N886" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:49 AM</t>
+        </is>
+      </c>
+      <c r="O886" s="2" t="inlineStr"/>
+      <c r="P886" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q886" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0886</t>
+        </is>
+      </c>
+      <c r="B887" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C887" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D887" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="E887" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F887" s="2" t="inlineStr"/>
+      <c r="G887" s="2" t="inlineStr"/>
+      <c r="H887" s="2" t="n">
+        <v>91732633</v>
+      </c>
+      <c r="I887" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J887" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K887" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105bd5</t>
+        </is>
+      </c>
+      <c r="L887" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M887" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B002 [Elec]</t>
+        </is>
+      </c>
+      <c r="N887" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:49 AM</t>
+        </is>
+      </c>
+      <c r="O887" s="2" t="inlineStr"/>
+      <c r="P887" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q887" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0887</t>
+        </is>
+      </c>
+      <c r="B888" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C888" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D888" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="E888" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F888" s="2" t="inlineStr"/>
+      <c r="G888" s="2" t="inlineStr"/>
+      <c r="H888" s="2" t="n">
+        <v>91732630</v>
+      </c>
+      <c r="I888" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J888" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K888" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105bd5</t>
+        </is>
+      </c>
+      <c r="L888" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M888" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B003 [Elec]</t>
+        </is>
+      </c>
+      <c r="N888" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:49 AM</t>
+        </is>
+      </c>
+      <c r="O888" s="2" t="inlineStr"/>
+      <c r="P888" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q888" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0888</t>
+        </is>
+      </c>
+      <c r="B889" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D889" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="E889" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="inlineStr"/>
+      <c r="G889" s="2" t="inlineStr"/>
+      <c r="H889" s="2" t="n">
+        <v>91732714</v>
+      </c>
+      <c r="I889" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J889" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K889" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105bd5</t>
+        </is>
+      </c>
+      <c r="L889" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M889" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B004 [Elec]</t>
+        </is>
+      </c>
+      <c r="N889" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:49 AM</t>
+        </is>
+      </c>
+      <c r="O889" s="2" t="inlineStr"/>
+      <c r="P889" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q889" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0889</t>
+        </is>
+      </c>
+      <c r="B890" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C890" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D890" s="2" t="inlineStr">
+        <is>
+          <t>B104</t>
+        </is>
+      </c>
+      <c r="E890" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F890" s="2" t="inlineStr"/>
+      <c r="G890" s="2" t="inlineStr"/>
+      <c r="H890" s="2" t="n">
+        <v>91732661</v>
+      </c>
+      <c r="I890" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J890" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K890" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105970</t>
+        </is>
+      </c>
+      <c r="L890" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M890" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B104 [Elec]</t>
+        </is>
+      </c>
+      <c r="N890" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 07:52 AM</t>
+        </is>
+      </c>
+      <c r="O890" s="2" t="inlineStr"/>
+      <c r="P890" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q890" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0890</t>
+        </is>
+      </c>
+      <c r="B891" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D891" s="2" t="inlineStr">
+        <is>
+          <t>B103</t>
+        </is>
+      </c>
+      <c r="E891" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F891" s="2" t="inlineStr"/>
+      <c r="G891" s="2" t="inlineStr"/>
+      <c r="H891" s="2" t="n">
+        <v>91732631</v>
+      </c>
+      <c r="I891" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J891" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K891" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105970</t>
+        </is>
+      </c>
+      <c r="L891" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M891" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B103 [Elec]</t>
+        </is>
+      </c>
+      <c r="N891" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 07:52 AM</t>
+        </is>
+      </c>
+      <c r="O891" s="2" t="inlineStr"/>
+      <c r="P891" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q891" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0891</t>
+        </is>
+      </c>
+      <c r="B892" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D892" s="2" t="inlineStr">
+        <is>
+          <t>B102</t>
+        </is>
+      </c>
+      <c r="E892" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F892" s="2" t="inlineStr"/>
+      <c r="G892" s="2" t="inlineStr"/>
+      <c r="H892" s="2" t="n">
+        <v>91732654</v>
+      </c>
+      <c r="I892" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J892" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K892" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105970</t>
+        </is>
+      </c>
+      <c r="L892" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M892" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B102 [Elec]</t>
+        </is>
+      </c>
+      <c r="N892" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 07:52 AM</t>
+        </is>
+      </c>
+      <c r="O892" s="2" t="inlineStr"/>
+      <c r="P892" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q892" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0892</t>
+        </is>
+      </c>
+      <c r="B893" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D893" s="2" t="inlineStr">
+        <is>
+          <t>B101</t>
+        </is>
+      </c>
+      <c r="E893" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="inlineStr"/>
+      <c r="G893" s="2" t="inlineStr"/>
+      <c r="H893" s="2" t="n">
+        <v>91732635</v>
+      </c>
+      <c r="I893" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J893" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K893" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105970</t>
+        </is>
+      </c>
+      <c r="L893" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M893" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B101 [Elec]</t>
+        </is>
+      </c>
+      <c r="N893" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 07:52 AM</t>
+        </is>
+      </c>
+      <c r="O893" s="2" t="inlineStr"/>
+      <c r="P893" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q893" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0893</t>
+        </is>
+      </c>
+      <c r="B894" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D894" s="2" t="inlineStr">
+        <is>
+          <t>A105</t>
+        </is>
+      </c>
+      <c r="E894" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F894" s="2" t="inlineStr"/>
+      <c r="G894" s="2" t="inlineStr"/>
+      <c r="H894" s="2" t="n">
+        <v>91732689</v>
+      </c>
+      <c r="I894" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J894" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K894" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105742</t>
+        </is>
+      </c>
+      <c r="L894" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M894" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A105 [Elec]</t>
+        </is>
+      </c>
+      <c r="N894" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:06 AM</t>
+        </is>
+      </c>
+      <c r="O894" s="2" t="inlineStr"/>
+      <c r="P894" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q894" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0894</t>
+        </is>
+      </c>
+      <c r="B895" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C895" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D895" s="2" t="inlineStr">
+        <is>
+          <t>A104</t>
+        </is>
+      </c>
+      <c r="E895" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F895" s="2" t="inlineStr"/>
+      <c r="G895" s="2" t="inlineStr"/>
+      <c r="H895" s="2" t="n">
+        <v>91732713</v>
+      </c>
+      <c r="I895" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J895" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K895" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105742</t>
+        </is>
+      </c>
+      <c r="L895" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M895" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A104 [Elec]</t>
+        </is>
+      </c>
+      <c r="N895" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:06 AM</t>
+        </is>
+      </c>
+      <c r="O895" s="2" t="inlineStr"/>
+      <c r="P895" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q895" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0895</t>
+        </is>
+      </c>
+      <c r="B896" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C896" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D896" s="2" t="inlineStr">
+        <is>
+          <t>A103</t>
+        </is>
+      </c>
+      <c r="E896" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F896" s="2" t="inlineStr"/>
+      <c r="G896" s="2" t="inlineStr"/>
+      <c r="H896" s="2" t="n">
+        <v>91732687</v>
+      </c>
+      <c r="I896" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J896" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K896" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105742</t>
+        </is>
+      </c>
+      <c r="L896" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M896" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A103 [Elec]</t>
+        </is>
+      </c>
+      <c r="N896" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:06 AM</t>
+        </is>
+      </c>
+      <c r="O896" s="2" t="inlineStr"/>
+      <c r="P896" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q896" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0896</t>
+        </is>
+      </c>
+      <c r="B897" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C897" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D897" s="2" t="inlineStr">
+        <is>
+          <t>A102</t>
+        </is>
+      </c>
+      <c r="E897" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F897" s="2" t="inlineStr"/>
+      <c r="G897" s="2" t="inlineStr"/>
+      <c r="H897" s="2" t="n">
+        <v>91732662</v>
+      </c>
+      <c r="I897" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J897" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K897" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105742</t>
+        </is>
+      </c>
+      <c r="L897" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M897" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A102 [Elec]</t>
+        </is>
+      </c>
+      <c r="N897" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:06 AM</t>
+        </is>
+      </c>
+      <c r="O897" s="2" t="inlineStr"/>
+      <c r="P897" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q897" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0897</t>
+        </is>
+      </c>
+      <c r="B898" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C898" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D898" s="2" t="inlineStr">
+        <is>
+          <t>A101</t>
+        </is>
+      </c>
+      <c r="E898" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F898" s="2" t="inlineStr"/>
+      <c r="G898" s="2" t="inlineStr"/>
+      <c r="H898" s="2" t="n">
+        <v>91732642</v>
+      </c>
+      <c r="I898" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J898" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K898" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105742</t>
+        </is>
+      </c>
+      <c r="L898" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M898" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A101 [Elec]</t>
+        </is>
+      </c>
+      <c r="N898" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:06 AM</t>
+        </is>
+      </c>
+      <c r="O898" s="2" t="inlineStr"/>
+      <c r="P898" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q898" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0898</t>
+        </is>
+      </c>
+      <c r="B899" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C899" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D899" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 01</t>
+        </is>
+      </c>
+      <c r="E899" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F899" s="2" t="inlineStr"/>
+      <c r="G899" s="2" t="inlineStr"/>
+      <c r="H899" s="2" t="n">
+        <v>91732982</v>
+      </c>
+      <c r="I899" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J899" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K899" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105678</t>
+        </is>
+      </c>
+      <c r="L899" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M899" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 1</t>
+        </is>
+      </c>
+      <c r="N899" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 07:49 AM</t>
+        </is>
+      </c>
+      <c r="O899" s="2" t="inlineStr"/>
+      <c r="P899" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q899" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0899</t>
+        </is>
+      </c>
+      <c r="B900" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C900" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D900" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 02</t>
+        </is>
+      </c>
+      <c r="E900" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F900" s="2" t="inlineStr"/>
+      <c r="G900" s="2" t="inlineStr"/>
+      <c r="H900" s="2" t="n">
+        <v>91733051</v>
+      </c>
+      <c r="I900" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J900" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K900" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105678</t>
+        </is>
+      </c>
+      <c r="L900" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M900" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 2</t>
+        </is>
+      </c>
+      <c r="N900" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 07:49 AM</t>
+        </is>
+      </c>
+      <c r="O900" s="2" t="inlineStr"/>
+      <c r="P900" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q900" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0900</t>
+        </is>
+      </c>
+      <c r="B901" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C901" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D901" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 03</t>
+        </is>
+      </c>
+      <c r="E901" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F901" s="2" t="inlineStr"/>
+      <c r="G901" s="2" t="inlineStr"/>
+      <c r="H901" s="2" t="n">
+        <v>91733028</v>
+      </c>
+      <c r="I901" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J901" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K901" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105678</t>
+        </is>
+      </c>
+      <c r="L901" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M901" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 3</t>
+        </is>
+      </c>
+      <c r="N901" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 07:49 AM</t>
+        </is>
+      </c>
+      <c r="O901" s="2" t="inlineStr"/>
+      <c r="P901" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q901" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0901</t>
+        </is>
+      </c>
+      <c r="B902" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C902" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D902" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 04</t>
+        </is>
+      </c>
+      <c r="E902" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F902" s="2" t="inlineStr"/>
+      <c r="G902" s="2" t="inlineStr"/>
+      <c r="H902" s="2" t="n">
+        <v>91733079</v>
+      </c>
+      <c r="I902" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J902" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K902" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105678</t>
+        </is>
+      </c>
+      <c r="L902" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M902" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 4</t>
+        </is>
+      </c>
+      <c r="N902" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 07:49 AM</t>
+        </is>
+      </c>
+      <c r="O902" s="2" t="inlineStr"/>
+      <c r="P902" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q902" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0902</t>
+        </is>
+      </c>
+      <c r="B903" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C903" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D903" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 14</t>
+        </is>
+      </c>
+      <c r="E903" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F903" s="2" t="inlineStr"/>
+      <c r="G903" s="2" t="inlineStr"/>
+      <c r="H903" s="2" t="n">
+        <v>91733024</v>
+      </c>
+      <c r="I903" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J903" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K903" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105678</t>
+        </is>
+      </c>
+      <c r="L903" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M903" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 14</t>
+        </is>
+      </c>
+      <c r="N903" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 07:49 AM</t>
+        </is>
+      </c>
+      <c r="O903" s="2" t="inlineStr"/>
+      <c r="P903" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q903" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0903</t>
+        </is>
+      </c>
+      <c r="B904" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C904" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D904" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 15</t>
+        </is>
+      </c>
+      <c r="E904" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F904" s="2" t="inlineStr"/>
+      <c r="G904" s="2" t="inlineStr"/>
+      <c r="H904" s="2" t="n">
+        <v>91733073</v>
+      </c>
+      <c r="I904" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J904" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K904" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105678</t>
+        </is>
+      </c>
+      <c r="L904" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M904" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 15</t>
+        </is>
+      </c>
+      <c r="N904" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:53 AM</t>
+        </is>
+      </c>
+      <c r="O904" s="2" t="inlineStr"/>
+      <c r="P904" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q904" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0904</t>
+        </is>
+      </c>
+      <c r="B905" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C905" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D905" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 16</t>
+        </is>
+      </c>
+      <c r="E905" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F905" s="2" t="inlineStr"/>
+      <c r="G905" s="2" t="inlineStr"/>
+      <c r="H905" s="2" t="n">
+        <v>91733029</v>
+      </c>
+      <c r="I905" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J905" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K905" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105678</t>
+        </is>
+      </c>
+      <c r="L905" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M905" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 16</t>
+        </is>
+      </c>
+      <c r="N905" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:53 AM</t>
+        </is>
+      </c>
+      <c r="O905" s="2" t="inlineStr"/>
+      <c r="P905" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q905" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0905</t>
+        </is>
+      </c>
+      <c r="B906" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C906" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D906" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 17</t>
+        </is>
+      </c>
+      <c r="E906" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F906" s="2" t="inlineStr"/>
+      <c r="G906" s="2" t="inlineStr"/>
+      <c r="H906" s="2" t="n">
+        <v>91733031</v>
+      </c>
+      <c r="I906" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J906" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K906" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105678</t>
+        </is>
+      </c>
+      <c r="L906" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M906" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 17</t>
+        </is>
+      </c>
+      <c r="N906" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:53 AM</t>
+        </is>
+      </c>
+      <c r="O906" s="2" t="inlineStr"/>
+      <c r="P906" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q906" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0906</t>
+        </is>
+      </c>
+      <c r="B907" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C907" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D907" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 18</t>
+        </is>
+      </c>
+      <c r="E907" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F907" s="2" t="inlineStr"/>
+      <c r="G907" s="2" t="inlineStr"/>
+      <c r="H907" s="2" t="n">
+        <v>91733022</v>
+      </c>
+      <c r="I907" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J907" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K907" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064105678</t>
+        </is>
+      </c>
+      <c r="L907" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M907" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 18</t>
+        </is>
+      </c>
+      <c r="N907" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:53 AM</t>
+        </is>
+      </c>
+      <c r="O907" s="2" t="inlineStr"/>
+      <c r="P907" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q907" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0907</t>
+        </is>
+      </c>
+      <c r="B908" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C908" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D908" s="2" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="E908" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F908" s="2" t="inlineStr"/>
+      <c r="G908" s="2" t="inlineStr"/>
+      <c r="H908" s="2" t="n">
+        <v>91732608</v>
+      </c>
+      <c r="I908" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J908" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K908" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064104e86</t>
+        </is>
+      </c>
+      <c r="L908" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M908" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A001 [Elec]</t>
+        </is>
+      </c>
+      <c r="N908" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:09 AM</t>
+        </is>
+      </c>
+      <c r="O908" s="2" t="inlineStr"/>
+      <c r="P908" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q908" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0908</t>
+        </is>
+      </c>
+      <c r="B909" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C909" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D909" s="2" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="E909" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F909" s="2" t="inlineStr"/>
+      <c r="G909" s="2" t="inlineStr"/>
+      <c r="H909" s="2" t="n">
+        <v>91732627</v>
+      </c>
+      <c r="I909" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J909" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K909" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064104e86</t>
+        </is>
+      </c>
+      <c r="L909" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M909" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A002 [Elec]</t>
+        </is>
+      </c>
+      <c r="N909" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:09 AM</t>
+        </is>
+      </c>
+      <c r="O909" s="2" t="inlineStr"/>
+      <c r="P909" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q909" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0909</t>
+        </is>
+      </c>
+      <c r="B910" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C910" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D910" s="2" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="E910" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F910" s="2" t="inlineStr"/>
+      <c r="G910" s="2" t="inlineStr"/>
+      <c r="H910" s="2" t="n">
+        <v>91732604</v>
+      </c>
+      <c r="I910" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J910" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K910" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064104e86</t>
+        </is>
+      </c>
+      <c r="L910" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M910" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A003 [Elec]</t>
+        </is>
+      </c>
+      <c r="N910" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:09 AM</t>
+        </is>
+      </c>
+      <c r="O910" s="2" t="inlineStr"/>
+      <c r="P910" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q910" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0910</t>
+        </is>
+      </c>
+      <c r="B911" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C911" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D911" s="2" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="E911" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F911" s="2" t="inlineStr"/>
+      <c r="G911" s="2" t="inlineStr"/>
+      <c r="H911" s="2" t="n">
+        <v>91732632</v>
+      </c>
+      <c r="I911" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J911" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K911" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064104e86</t>
+        </is>
+      </c>
+      <c r="L911" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M911" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A004 [Elec]</t>
+        </is>
+      </c>
+      <c r="N911" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:09 AM</t>
+        </is>
+      </c>
+      <c r="O911" s="2" t="inlineStr"/>
+      <c r="P911" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q911" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0911</t>
+        </is>
+      </c>
+      <c r="B912" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C912" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D912" s="2" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="E912" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F912" s="2" t="inlineStr"/>
+      <c r="G912" s="2" t="inlineStr"/>
+      <c r="H912" s="2" t="n">
+        <v>91732606</v>
+      </c>
+      <c r="I912" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J912" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K912" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f12064104e86</t>
+        </is>
+      </c>
+      <c r="L912" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M912" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A005 [Elec]</t>
+        </is>
+      </c>
+      <c r="N912" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:09 AM</t>
+        </is>
+      </c>
+      <c r="O912" s="2" t="inlineStr"/>
+      <c r="P912" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q912" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0912</t>
+        </is>
+      </c>
+      <c r="B913" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C913" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D913" s="2" t="inlineStr">
+        <is>
+          <t>B204</t>
+        </is>
+      </c>
+      <c r="E913" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F913" s="2" t="inlineStr"/>
+      <c r="G913" s="2" t="inlineStr"/>
+      <c r="H913" s="2" t="n">
+        <v>91732609</v>
+      </c>
+      <c r="I913" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J913" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K913" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350168b</t>
+        </is>
+      </c>
+      <c r="L913" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M913" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B204 [Elec]</t>
+        </is>
+      </c>
+      <c r="N913" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:23 AM</t>
+        </is>
+      </c>
+      <c r="O913" s="2" t="inlineStr"/>
+      <c r="P913" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q913" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0913</t>
+        </is>
+      </c>
+      <c r="B914" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C914" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D914" s="2" t="inlineStr">
+        <is>
+          <t>B203</t>
+        </is>
+      </c>
+      <c r="E914" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F914" s="2" t="inlineStr"/>
+      <c r="G914" s="2" t="inlineStr"/>
+      <c r="H914" s="2" t="n">
+        <v>91732712</v>
+      </c>
+      <c r="I914" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J914" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K914" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350168b</t>
+        </is>
+      </c>
+      <c r="L914" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M914" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B203 [Elec]</t>
+        </is>
+      </c>
+      <c r="N914" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:23 AM</t>
+        </is>
+      </c>
+      <c r="O914" s="2" t="inlineStr"/>
+      <c r="P914" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q914" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0914</t>
+        </is>
+      </c>
+      <c r="B915" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C915" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D915" s="2" t="inlineStr">
+        <is>
+          <t>B202</t>
+        </is>
+      </c>
+      <c r="E915" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F915" s="2" t="inlineStr"/>
+      <c r="G915" s="2" t="inlineStr"/>
+      <c r="H915" s="2" t="n">
+        <v>91732629</v>
+      </c>
+      <c r="I915" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J915" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K915" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350168b</t>
+        </is>
+      </c>
+      <c r="L915" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M915" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B202 [Elec]</t>
+        </is>
+      </c>
+      <c r="N915" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:23 AM</t>
+        </is>
+      </c>
+      <c r="O915" s="2" t="inlineStr"/>
+      <c r="P915" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q915" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0915</t>
+        </is>
+      </c>
+      <c r="B916" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C916" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="D916" s="2" t="inlineStr">
+        <is>
+          <t>B201</t>
+        </is>
+      </c>
+      <c r="E916" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F916" s="2" t="inlineStr"/>
+      <c r="G916" s="2" t="inlineStr"/>
+      <c r="H916" s="2" t="n">
+        <v>91732690</v>
+      </c>
+      <c r="I916" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J916" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K916" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350168b</t>
+        </is>
+      </c>
+      <c r="L916" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M916" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove B201 [Elec]</t>
+        </is>
+      </c>
+      <c r="N916" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:23 AM</t>
+        </is>
+      </c>
+      <c r="O916" s="2" t="inlineStr"/>
+      <c r="P916" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q916" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-B-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0916</t>
+        </is>
+      </c>
+      <c r="B917" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C917" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D917" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 06</t>
+        </is>
+      </c>
+      <c r="E917" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F917" s="2" t="inlineStr"/>
+      <c r="G917" s="2" t="inlineStr"/>
+      <c r="H917" s="2" t="n">
+        <v>91733075</v>
+      </c>
+      <c r="I917" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J917" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K917" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350128a</t>
+        </is>
+      </c>
+      <c r="L917" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M917" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 06</t>
+        </is>
+      </c>
+      <c r="N917" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:47 AM</t>
+        </is>
+      </c>
+      <c r="O917" s="2" t="inlineStr"/>
+      <c r="P917" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q917" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet; label duplicated in AMR export (check which is DB 05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0917</t>
+        </is>
+      </c>
+      <c r="B918" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C918" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D918" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 06</t>
+        </is>
+      </c>
+      <c r="E918" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F918" s="2" t="inlineStr"/>
+      <c r="G918" s="2" t="inlineStr"/>
+      <c r="H918" s="2" t="n">
+        <v>91732873</v>
+      </c>
+      <c r="I918" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J918" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K918" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350128a</t>
+        </is>
+      </c>
+      <c r="L918" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M918" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 06</t>
+        </is>
+      </c>
+      <c r="N918" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:47 AM</t>
+        </is>
+      </c>
+      <c r="O918" s="2" t="inlineStr"/>
+      <c r="P918" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q918" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet; label duplicated in AMR export (check which is DB 05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0918</t>
+        </is>
+      </c>
+      <c r="B919" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C919" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D919" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 07</t>
+        </is>
+      </c>
+      <c r="E919" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F919" s="2" t="inlineStr"/>
+      <c r="G919" s="2" t="inlineStr"/>
+      <c r="H919" s="2" t="n">
+        <v>91732860</v>
+      </c>
+      <c r="I919" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J919" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K919" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350128a</t>
+        </is>
+      </c>
+      <c r="L919" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M919" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 07</t>
+        </is>
+      </c>
+      <c r="N919" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:47 AM</t>
+        </is>
+      </c>
+      <c r="O919" s="2" t="inlineStr"/>
+      <c r="P919" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q919" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0919</t>
+        </is>
+      </c>
+      <c r="B920" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C920" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D920" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 08</t>
+        </is>
+      </c>
+      <c r="E920" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F920" s="2" t="inlineStr"/>
+      <c r="G920" s="2" t="inlineStr"/>
+      <c r="H920" s="2" t="n">
+        <v>91732856</v>
+      </c>
+      <c r="I920" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J920" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K920" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350128a</t>
+        </is>
+      </c>
+      <c r="L920" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M920" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 08</t>
+        </is>
+      </c>
+      <c r="N920" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:47 AM</t>
+        </is>
+      </c>
+      <c r="O920" s="2" t="inlineStr"/>
+      <c r="P920" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q920" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0920</t>
+        </is>
+      </c>
+      <c r="B921" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C921" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D921" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 09</t>
+        </is>
+      </c>
+      <c r="E921" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F921" s="2" t="inlineStr"/>
+      <c r="G921" s="2" t="inlineStr"/>
+      <c r="H921" s="2" t="n">
+        <v>91732875</v>
+      </c>
+      <c r="I921" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J921" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K921" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350128a</t>
+        </is>
+      </c>
+      <c r="L921" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M921" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 09</t>
+        </is>
+      </c>
+      <c r="N921" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:47 AM</t>
+        </is>
+      </c>
+      <c r="O921" s="2" t="inlineStr"/>
+      <c r="P921" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q921" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0921</t>
+        </is>
+      </c>
+      <c r="B922" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C922" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D922" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 10</t>
+        </is>
+      </c>
+      <c r="E922" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F922" s="2" t="inlineStr"/>
+      <c r="G922" s="2" t="inlineStr"/>
+      <c r="H922" s="2" t="n">
+        <v>91732876</v>
+      </c>
+      <c r="I922" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J922" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K922" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350128a</t>
+        </is>
+      </c>
+      <c r="L922" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M922" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 10</t>
+        </is>
+      </c>
+      <c r="N922" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:47 AM</t>
+        </is>
+      </c>
+      <c r="O922" s="2" t="inlineStr"/>
+      <c r="P922" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q922" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0922</t>
+        </is>
+      </c>
+      <c r="B923" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C923" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D923" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 11</t>
+        </is>
+      </c>
+      <c r="E923" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F923" s="2" t="inlineStr"/>
+      <c r="G923" s="2" t="inlineStr"/>
+      <c r="H923" s="2" t="n">
+        <v>91732913</v>
+      </c>
+      <c r="I923" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J923" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K923" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350128a</t>
+        </is>
+      </c>
+      <c r="L923" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M923" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 11</t>
+        </is>
+      </c>
+      <c r="N923" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:47 AM</t>
+        </is>
+      </c>
+      <c r="O923" s="2" t="inlineStr"/>
+      <c r="P923" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q923" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0923</t>
+        </is>
+      </c>
+      <c r="B924" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C924" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D924" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 12</t>
+        </is>
+      </c>
+      <c r="E924" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F924" s="2" t="inlineStr"/>
+      <c r="G924" s="2" t="inlineStr"/>
+      <c r="H924" s="2" t="n">
+        <v>91732886</v>
+      </c>
+      <c r="I924" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J924" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K924" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350128a</t>
+        </is>
+      </c>
+      <c r="L924" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M924" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 12</t>
+        </is>
+      </c>
+      <c r="N924" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:47 AM</t>
+        </is>
+      </c>
+      <c r="O924" s="2" t="inlineStr"/>
+      <c r="P924" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q924" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0924</t>
+        </is>
+      </c>
+      <c r="B925" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C925" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="D925" s="2" t="inlineStr">
+        <is>
+          <t>FF DB 13</t>
+        </is>
+      </c>
+      <c r="E925" s="2" t="inlineStr">
+        <is>
+          <t>Common / other</t>
+        </is>
+      </c>
+      <c r="F925" s="2" t="inlineStr"/>
+      <c r="G925" s="2" t="inlineStr"/>
+      <c r="H925" s="2" t="n">
+        <v>91732902</v>
+      </c>
+      <c r="I925" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J925" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K925" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350128a</t>
+        </is>
+      </c>
+      <c r="L925" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M925" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove FF DB 13</t>
+        </is>
+      </c>
+      <c r="N925" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:47 AM</t>
+        </is>
+      </c>
+      <c r="O925" s="2" t="inlineStr"/>
+      <c r="P925" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q925" s="2" t="inlineStr">
+        <is>
+          <t>Added from AMR export (serial-keyed) – kiosk not in reticulation sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0925</t>
+        </is>
+      </c>
+      <c r="B926" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C926" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D926" s="2" t="inlineStr">
+        <is>
+          <t>A205</t>
+        </is>
+      </c>
+      <c r="E926" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F926" s="2" t="inlineStr"/>
+      <c r="G926" s="2" t="inlineStr"/>
+      <c r="H926" s="2" t="n">
+        <v>91732688</v>
+      </c>
+      <c r="I926" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J926" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K926" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635003ed</t>
+        </is>
+      </c>
+      <c r="L926" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M926" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A205 [Elec]</t>
+        </is>
+      </c>
+      <c r="N926" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:23 AM</t>
+        </is>
+      </c>
+      <c r="O926" s="2" t="inlineStr"/>
+      <c r="P926" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q926" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0926</t>
+        </is>
+      </c>
+      <c r="B927" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C927" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D927" s="2" t="inlineStr">
+        <is>
+          <t>A204</t>
+        </is>
+      </c>
+      <c r="E927" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F927" s="2" t="inlineStr"/>
+      <c r="G927" s="2" t="inlineStr"/>
+      <c r="H927" s="2" t="n">
+        <v>91732637</v>
+      </c>
+      <c r="I927" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J927" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K927" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635003ed</t>
+        </is>
+      </c>
+      <c r="L927" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M927" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A204 [Elec]</t>
+        </is>
+      </c>
+      <c r="N927" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:23 AM</t>
+        </is>
+      </c>
+      <c r="O927" s="2" t="inlineStr"/>
+      <c r="P927" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q927" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0927</t>
+        </is>
+      </c>
+      <c r="B928" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C928" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D928" s="2" t="inlineStr">
+        <is>
+          <t>A203</t>
+        </is>
+      </c>
+      <c r="E928" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F928" s="2" t="inlineStr"/>
+      <c r="G928" s="2" t="inlineStr"/>
+      <c r="H928" s="2" t="n">
+        <v>91732636</v>
+      </c>
+      <c r="I928" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J928" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K928" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635003ed</t>
+        </is>
+      </c>
+      <c r="L928" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M928" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A203 [Elec]</t>
+        </is>
+      </c>
+      <c r="N928" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:23 AM</t>
+        </is>
+      </c>
+      <c r="O928" s="2" t="inlineStr"/>
+      <c r="P928" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q928" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0928</t>
+        </is>
+      </c>
+      <c r="B929" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C929" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D929" s="2" t="inlineStr">
+        <is>
+          <t>A202</t>
+        </is>
+      </c>
+      <c r="E929" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F929" s="2" t="inlineStr"/>
+      <c r="G929" s="2" t="inlineStr"/>
+      <c r="H929" s="2" t="n">
+        <v>91732658</v>
+      </c>
+      <c r="I929" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J929" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K929" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635003ed</t>
+        </is>
+      </c>
+      <c r="L929" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M929" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A202 [Elec]</t>
+        </is>
+      </c>
+      <c r="N929" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:23 AM</t>
+        </is>
+      </c>
+      <c r="O929" s="2" t="inlineStr"/>
+      <c r="P929" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q929" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="2" t="inlineStr">
+        <is>
+          <t>ZLM-0929</t>
+        </is>
+      </c>
+      <c r="B930" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="C930" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="D930" s="2" t="inlineStr">
+        <is>
+          <t>A201</t>
+        </is>
+      </c>
+      <c r="E930" s="2" t="inlineStr">
+        <is>
+          <t>Stand</t>
+        </is>
+      </c>
+      <c r="F930" s="2" t="inlineStr"/>
+      <c r="G930" s="2" t="inlineStr"/>
+      <c r="H930" s="2" t="n">
+        <v>91732614</v>
+      </c>
+      <c r="I930" s="2" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="J930" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K930" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635003ed</t>
+        </is>
+      </c>
+      <c r="L930" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M930" s="2" t="inlineStr">
+        <is>
+          <t>Coral Cove A201 [Elec]</t>
+        </is>
+      </c>
+      <c r="N930" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 09:23 AM</t>
+        </is>
+      </c>
+      <c r="O930" s="2" t="inlineStr"/>
+      <c r="P930" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+      <c r="Q930" s="2" t="inlineStr">
+        <is>
+          <t>Flat behind DB-A-01 – added from AMR export (serial-keyed)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q885"/>
+  <autoFilter ref="A1:Q930"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53485,7 +57444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q189"/>
+  <dimension ref="A1:Q192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -66470,8 +70429,187 @@
         </is>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block A flats</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Meter panel / DB</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>K 2,4 – Block A</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>DB-A-01</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Assumed (behind block DB)</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr"/>
+      <c r="I190" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120635003ed, 2cf7f12064104e86, 2cf7f12064105742</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr"/>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>Installed</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr"/>
+      <c r="O190" s="2" t="inlineStr"/>
+      <c r="P190" s="2" t="inlineStr"/>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Coral Block B flats</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Meter panel / DB</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>K 2,3 – Block B</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>DB-B-01</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Assumed (behind block DB)</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
+      <c r="I191" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350168b, 2cf7f12064105970, 2cf7f12064105bd5</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="inlineStr"/>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>Installed</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr"/>
+      <c r="O191" s="2" t="inlineStr"/>
+      <c r="P191" s="2" t="inlineStr"/>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Coral FF DBs</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Meter panel / DB</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed – not in reticulation sheet</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr"/>
+      <c r="I192" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206350128a, 2cf7f12064105678</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr"/>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>Installed</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr"/>
+      <c r="O192" s="2" t="inlineStr"/>
+      <c r="P192" s="2" t="inlineStr"/>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>AMR export 09 Oct 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q189"/>
+  <autoFilter ref="A1:Q192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -66758,11 +70896,19 @@
       <c r="F5" s="2" t="n">
         <v>90915109</v>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f1206340076e</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:43 AM</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -66806,11 +70952,19 @@
       <c r="F6" s="2" t="n">
         <v>91074243</v>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2cf7f120634007d5</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10/9/2026, 08:50 AM</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -68080,7 +72234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -68774,22 +72928,88 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>AMR export</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>MS 04 / MS 05</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Coral minisub bulk meters (90915109, 91074243) are not on AMR. → now on AMR (export 09 Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AMR export</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>"Coral Cove FF DB 06" appears twice (91733075, 91732873) and FF DB 05 is missing – one label is probably wrong. FF DB location not in reticulation sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>AMR export</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>MS 04 / MS 05</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Coral minisub bulk meters (90915109, 91074243) are not on AMR.</t>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>"Coral Cove 1xx" (device …5981 port 1, serial 91732851xx) not added – placeholder serial; 91732851 is already stand 186 on port 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MS 05</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>45 Coral Cove meters added from the AMR export on 09 Oct 2026 (Block A/B flats and FF DBs), keyed on meter serial.</t>
         </is>
       </c>
     </row>
